--- a/Data/Config.xlsx
+++ b/Data/Config.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\uidt0706\Documents\UiPath\AU_EU_DE_SCM_UPLOAD_PICKUP_CONFIRMATION_3\Data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\uidt0706\Documents\UiPath\EU_DE_RBG_ANS_SCM_UploadPickupConfirmation\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D0D5DD3B-D6C8-416F-8AB9-F7C0E4D670E2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2B2EBC0C-D863-4904-83BB-99D3546867BB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="750" yWindow="3930" windowWidth="21600" windowHeight="11385" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3405" yWindow="1410" windowWidth="21600" windowHeight="11385" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Settings" sheetId="1" r:id="rId1"/>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="64" uniqueCount="50">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="66" uniqueCount="51">
   <si>
     <t>Name</t>
   </si>
@@ -172,10 +172,13 @@
     <t>AU_EU_DE_SCM_UPLOAD_PICKUP_CONFIRMATION_SAP_User01</t>
   </si>
   <si>
-    <t xml:space="preserve"> </t>
-  </si>
-  <si>
-    <t>AU_EU_DE_SCM_UPLOAD_PICKUP_CONFIRMATION</t>
+    <t>OrchestratorQueueName2</t>
+  </si>
+  <si>
+    <t>EU_DE_RBG_ANS_SCM_UploadPickupConfirmation</t>
+  </si>
+  <si>
+    <t>EU_DE_RBG_ANS_SCM_UploadPickupConfirmationSAP</t>
   </si>
 </sst>
 </file>
@@ -577,8 +580,8 @@
   <sheetFormatPr defaultColWidth="14.42578125" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="43.5703125" customWidth="1"/>
-    <col min="2" max="2" width="48.42578125" customWidth="1"/>
-    <col min="3" max="3" width="81.42578125" customWidth="1"/>
+    <col min="2" max="2" width="50.42578125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="88.7109375" bestFit="1" customWidth="1"/>
     <col min="4" max="26" width="8.7109375" customWidth="1"/>
   </cols>
   <sheetData>
@@ -652,8 +655,14 @@
     </row>
     <row r="6" spans="1:26" ht="14.25" customHeight="1"/>
     <row r="7" spans="1:26" ht="14.25" customHeight="1">
-      <c r="B7" t="s">
+      <c r="A7" s="2" t="s">
         <v>48</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>22</v>
       </c>
     </row>
     <row r="8" spans="1:26" ht="14.25" customHeight="1"/>

--- a/Data/Config.xlsx
+++ b/Data/Config.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\uidt0706\Documents\UiPath\EU_DE_RBG_ANS_SCM_UploadPickupConfirmation\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2B2EBC0C-D863-4904-83BB-99D3546867BB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D0B29555-A231-406A-990E-4DB8AFEC955C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3405" yWindow="1410" windowWidth="21600" windowHeight="11385" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3405" yWindow="1410" windowWidth="21600" windowHeight="11385" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Settings" sheetId="1" r:id="rId1"/>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="66" uniqueCount="51">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="57" uniqueCount="48">
   <si>
     <t>Name</t>
   </si>
@@ -160,16 +160,7 @@
     <t xml:space="preserve">The maximum number of consecutive system exceptions was reached. </t>
   </si>
   <si>
-    <t>AU_EU_DE_SCM_UPLOAD_PICKUP_CONFIRMATION_SAP_Mandant</t>
-  </si>
-  <si>
-    <t>AU_EU_DE_SCM_UPLOAD_PICKUP_CONFIRMATION_SAP_System</t>
-  </si>
-  <si>
     <t>AUTO/AN/Regensburg/SCM</t>
-  </si>
-  <si>
-    <t>AU_EU_DE_SCM_UPLOAD_PICKUP_CONFIRMATION_SAP_User01</t>
   </si>
   <si>
     <t>OrchestratorQueueName2</t>
@@ -624,7 +615,7 @@
         <v>24</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="C2" s="2" t="s">
         <v>22</v>
@@ -635,7 +626,7 @@
         <v>31</v>
       </c>
       <c r="B3" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="C3" s="4" t="s">
         <v>32</v>
@@ -656,10 +647,10 @@
     <row r="6" spans="1:26" ht="14.25" customHeight="1"/>
     <row r="7" spans="1:26" ht="14.25" customHeight="1">
       <c r="A7" s="2" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="C7" s="2" t="s">
         <v>22</v>
@@ -2874,28 +2865,8 @@
       <c r="Y1" s="1"/>
       <c r="Z1" s="1"/>
     </row>
-    <row r="2" spans="1:26" ht="14.25" customHeight="1">
-      <c r="A2" t="s">
-        <v>44</v>
-      </c>
-      <c r="B2" t="s">
-        <v>44</v>
-      </c>
-      <c r="C2" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="3" spans="1:26" ht="14.25" customHeight="1">
-      <c r="A3" t="s">
-        <v>45</v>
-      </c>
-      <c r="B3" t="s">
-        <v>45</v>
-      </c>
-      <c r="C3" t="s">
-        <v>46</v>
-      </c>
-    </row>
+    <row r="2" spans="1:26" ht="14.25" customHeight="1"/>
+    <row r="3" spans="1:26" ht="14.25" customHeight="1"/>
     <row r="4" spans="1:26" ht="14.25" customHeight="1"/>
     <row r="5" spans="1:26" ht="14.25" customHeight="1"/>
     <row r="6" spans="1:26" ht="14.25" customHeight="1"/>
@@ -3947,17 +3918,7 @@
       <c r="Y1" s="1"/>
       <c r="Z1" s="1"/>
     </row>
-    <row r="2" spans="1:26" ht="14.25" customHeight="1">
-      <c r="A2" t="s">
-        <v>47</v>
-      </c>
-      <c r="B2" t="s">
-        <v>47</v>
-      </c>
-      <c r="C2" t="s">
-        <v>46</v>
-      </c>
-    </row>
+    <row r="2" spans="1:26" ht="14.25" customHeight="1"/>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
